--- a/KatalonData/EmailTextToPay/Manage_EmailText.xlsx
+++ b/KatalonData/EmailTextToPay/Manage_EmailText.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="270">
   <si>
     <t>Result</t>
   </si>
@@ -434,6 +434,519 @@
   </si>
   <si>
     <t>Mon May 18 21:13:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 17:47:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 17:49:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 17:51:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 17:52:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 17:54:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 17:54:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 17:57:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:01:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:02:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:02:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:03:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:04:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:04:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:05:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:06:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:07:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:07:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:10:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:11:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:11:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:12:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:13:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:14:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:17:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:18:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:19:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:20:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:21:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:22:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:23:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:24:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:25:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:25:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:29:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:30:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:30:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:32:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:33:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:34:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:35:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:35:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:36:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:37:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:38:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:39:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:40:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:40:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:41:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:44:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:45:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:46:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:47:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:48:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:49:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:51:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:52:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:54:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:55:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:57:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 18:59:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 19:00:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 19:00:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:34:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:35:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:36:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:36:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:37:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:38:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:38:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:39:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:40:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:41:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:41:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:42:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:43:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:43:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:44:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:45:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:46:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:46:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:47:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:48:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:48:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:49:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:50:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:51:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:51:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:52:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:53:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:53:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:54:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:55:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:56:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:56:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:57:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:58:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:59:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:59:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:00:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:01:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:02:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:03:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:03:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:04:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:05:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:06:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:06:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:07:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:08:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:09:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:10:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:11:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:11:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:12:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:13:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:14:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:14:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:15:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:16:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:17:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:18:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:18:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:19:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:20:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:21:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:21:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:22:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:23:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:23:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:24:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:09:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:11:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:12:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:13:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:14:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:14:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:15:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:16:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:17:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:17:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:18:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:19:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:20:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:21:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:22:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:22:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:23:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:24:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:25:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:26:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:27:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:28:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:29:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:31:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:32:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:34:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:36:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:38:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:39:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:41:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:42:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:43:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:44:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:46:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:47:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:49:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:50:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:51:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:53:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:54:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:54:19 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -975,7 +1488,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>268</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>62</v>
@@ -992,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>269</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>62</v>
@@ -1058,7 +1571,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>255</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -1114,7 +1627,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>231</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>
@@ -1170,7 +1683,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>232</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>
@@ -1226,7 +1739,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>
@@ -1289,7 +1802,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>241</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>33</v>
@@ -1310,7 +1823,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>242</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>34</v>
@@ -1337,7 +1850,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>243</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>29</v>
@@ -1360,7 +1873,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>244</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>30</v>
@@ -1383,7 +1896,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>245</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>31</v>
@@ -1406,7 +1919,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>246</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>32</v>
@@ -1429,7 +1942,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>247</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>44</v>
@@ -1452,7 +1965,7 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>248</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>45</v>
@@ -1475,7 +1988,7 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>249</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>46</v>
@@ -1541,7 +2054,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>233</v>
       </c>
       <c r="C2" s="18" t="s">
         <v>37</v>
@@ -1567,7 +2080,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>234</v>
       </c>
       <c r="C4" s="18" t="s">
         <v>40</v>
@@ -1587,7 +2100,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>235</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>41</v>
@@ -1607,7 +2120,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>42</v>
@@ -1630,7 +2143,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>22</v>
@@ -1653,7 +2166,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>238</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>23</v>
@@ -1676,7 +2189,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>239</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>24</v>
@@ -1703,7 +2216,7 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>39</v>
@@ -1781,7 +2294,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>260</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>49</v>
@@ -1858,7 +2371,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>50</v>
@@ -1935,7 +2448,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>259</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>51</v>
@@ -2012,7 +2525,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>257</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>11</v>
@@ -2089,7 +2602,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>258</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>12</v>
@@ -2166,7 +2679,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>256</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>13</v>
@@ -2223,7 +2736,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>265</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>14</v>
@@ -2292,7 +2805,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>267</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>56</v>
@@ -2361,7 +2874,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>262</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>57</v>
@@ -2426,7 +2939,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -2482,7 +2995,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>251</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>

--- a/KatalonData/EmailTextToPay/Manage_EmailText.xlsx
+++ b/KatalonData/EmailTextToPay/Manage_EmailText.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="275">
   <si>
     <t>Result</t>
   </si>
@@ -947,6 +947,21 @@
   </si>
   <si>
     <t>Thu Jun 18 03:54:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 26 21:05:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 26 21:05:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 26 22:38:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 21:09:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 21:10:17 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1488,7 +1503,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>62</v>
@@ -1505,7 +1520,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>62</v>
@@ -2525,7 +2540,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>11</v>

--- a/KatalonData/EmailTextToPay/Manage_EmailText.xlsx
+++ b/KatalonData/EmailTextToPay/Manage_EmailText.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="317">
   <si>
     <t>Result</t>
   </si>
@@ -962,6 +962,132 @@
   </si>
   <si>
     <t>Tue Jun 30 21:10:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 18:24:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 18:47:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:16:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:17:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:18:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:19:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:20:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:21:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:22:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:22:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:23:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:24:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:25:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:25:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:26:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:27:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:28:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:28:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:29:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:30:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:30:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:31:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:31:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:32:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:33:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:34:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:35:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:36:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:37:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:38:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:39:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:40:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:41:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:42:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:43:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:44:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:45:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:46:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:47:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:48:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:49:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:49:39 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1470,7 +1596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="19" width="6.26953125" collapsed="true"/>
@@ -1499,11 +1625,11 @@
       </c>
     </row>
     <row ht="13" r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>273</v>
+      <c r="A2" t="s" s="19">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="26">
+        <v>315</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>62</v>
@@ -1516,11 +1642,11 @@
       </c>
     </row>
     <row ht="13" r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>274</v>
+      <c r="A3" t="s" s="19">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s" s="26">
+        <v>316</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>62</v>
@@ -1552,7 +1678,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB20ABE5-EB40-4301-BBE4-8B897354D04D}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.81640625" collapsed="true"/>
@@ -1582,11 +1708,11 @@
       </c>
     </row>
     <row customFormat="1" ht="75" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>255</v>
+      <c r="A2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>302</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -1608,7 +1734,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03671AC8-56DE-457F-802A-D25D162F1818}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.1796875" collapsed="true"/>
@@ -1638,11 +1764,11 @@
       </c>
     </row>
     <row customFormat="1" ht="150" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>231</v>
+      <c r="A2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>278</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>
@@ -1664,7 +1790,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C8D7B23-96A3-4C14-84F1-69CBEB776D28}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.1796875" collapsed="true"/>
@@ -1694,11 +1820,11 @@
       </c>
     </row>
     <row customFormat="1" ht="150" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>232</v>
+      <c r="A2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>282</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>
@@ -1720,7 +1846,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EEFB455-878E-4283-8CDF-5280F5D2D976}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.1796875" collapsed="true"/>
@@ -1750,11 +1876,11 @@
       </c>
     </row>
     <row customFormat="1" ht="150" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>229</v>
+      <c r="A2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>277</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>
@@ -1776,7 +1902,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAC7F82F-C603-4F07-8548-EF17D188B148}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="1" width="8.7265625" collapsed="true"/>
@@ -1813,11 +1939,11 @@
       </c>
     </row>
     <row customHeight="1" ht="51.5" r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>241</v>
+      <c r="A2" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="1">
+        <v>291</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>33</v>
@@ -1834,11 +1960,11 @@
       <c r="E3" s="5"/>
     </row>
     <row ht="62.5" r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>242</v>
+      <c r="A4" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>292</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>34</v>
@@ -1861,11 +1987,11 @@
       <c r="E5" s="5"/>
     </row>
     <row ht="75" r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>243</v>
+      <c r="A6" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s" s="1">
+        <v>293</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>29</v>
@@ -1884,11 +2010,11 @@
       </c>
     </row>
     <row ht="62.5" r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>244</v>
+      <c r="A7" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s" s="1">
+        <v>294</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>30</v>
@@ -1907,11 +2033,11 @@
       </c>
     </row>
     <row ht="75" r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>245</v>
+      <c r="A8" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s" s="1">
+        <v>295</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>31</v>
@@ -1930,11 +2056,11 @@
       </c>
     </row>
     <row ht="75" r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>246</v>
+      <c r="A9" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s" s="1">
+        <v>296</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>32</v>
@@ -1953,11 +2079,11 @@
       </c>
     </row>
     <row ht="62.5" r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
-        <v>247</v>
+      <c r="A10" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s" s="1">
+        <v>297</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>44</v>
@@ -1976,11 +2102,11 @@
       </c>
     </row>
     <row ht="62.5" r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
-        <v>248</v>
+      <c r="A11" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s" s="1">
+        <v>298</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>45</v>
@@ -1999,11 +2125,11 @@
       </c>
     </row>
     <row ht="62.5" r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>249</v>
+      <c r="A12" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s" s="1">
+        <v>299</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>46</v>
@@ -2028,7 +2154,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E26A7E4-F23A-4B0C-8BC6-AFD45C94E0CE}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="1" width="8.7265625" collapsed="true"/>
@@ -2065,11 +2191,11 @@
       </c>
     </row>
     <row ht="62.5" r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>233</v>
+      <c r="A2" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="1">
+        <v>283</v>
       </c>
       <c r="C2" s="18" t="s">
         <v>37</v>
@@ -2091,11 +2217,11 @@
       <c r="F3" s="5"/>
     </row>
     <row ht="62.5" r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>234</v>
+      <c r="A4" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>284</v>
       </c>
       <c r="C4" s="18" t="s">
         <v>40</v>
@@ -2111,11 +2237,11 @@
       </c>
     </row>
     <row ht="62.5" r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>235</v>
+      <c r="A5" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s" s="1">
+        <v>285</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>41</v>
@@ -2131,11 +2257,11 @@
       </c>
     </row>
     <row ht="62.5" r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>236</v>
+      <c r="A6" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s" s="1">
+        <v>286</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>42</v>
@@ -2154,11 +2280,11 @@
       <c r="C7" s="4"/>
     </row>
     <row customHeight="1" ht="55" r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>237</v>
+      <c r="A8" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s" s="1">
+        <v>287</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>22</v>
@@ -2177,11 +2303,11 @@
       </c>
     </row>
     <row customHeight="1" ht="55" r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>238</v>
+      <c r="A9" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s" s="1">
+        <v>288</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>23</v>
@@ -2200,11 +2326,11 @@
       </c>
     </row>
     <row customHeight="1" ht="55" r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
-        <v>239</v>
+      <c r="A10" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s" s="1">
+        <v>289</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>24</v>
@@ -2227,11 +2353,11 @@
       <c r="E11" s="5"/>
     </row>
     <row ht="50" r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>240</v>
+      <c r="A12" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s" s="1">
+        <v>290</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>39</v>
@@ -2255,7 +2381,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B68FE70-BD03-498B-B600-6B4B7C132BA1}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="16" width="7.26953125" collapsed="true"/>
@@ -2305,16 +2431,16 @@
       </c>
     </row>
     <row customFormat="1" ht="38" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>260</v>
+      <c r="A2" t="s" s="16">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="16">
+        <v>307</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="16">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
@@ -2332,7 +2458,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EABB53-51F5-4A90-B8E2-ADBC54583C91}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="16" width="7.26953125" collapsed="true"/>
@@ -2382,16 +2508,16 @@
       </c>
     </row>
     <row customFormat="1" ht="38" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>261</v>
+      <c r="A2" t="s" s="16">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="16">
+        <v>308</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="16">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
@@ -2409,7 +2535,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DD67883-E46D-4766-8983-E96E92BD2427}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="16" width="7.26953125" collapsed="true"/>
@@ -2459,16 +2585,16 @@
       </c>
     </row>
     <row customFormat="1" ht="38" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>259</v>
+      <c r="A2" t="s" s="16">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="16">
+        <v>306</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="16">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
@@ -2486,7 +2612,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="16" width="7.26953125" collapsed="true"/>
@@ -2536,16 +2662,16 @@
       </c>
     </row>
     <row customFormat="1" ht="25.5" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>272</v>
+      <c r="A2" t="s" s="16">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="16">
+        <v>304</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="16">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
@@ -2563,7 +2689,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DBD4D3F-6789-4F69-A50C-D0C16059C617}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
@@ -2613,16 +2739,16 @@
       </c>
     </row>
     <row customFormat="1" ht="38" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>258</v>
+      <c r="A2" t="s" s="6">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="6">
+        <v>305</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="6">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
@@ -2640,7 +2766,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D6A91F-B4A5-4069-ABF9-05ADE24D338D}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
@@ -2690,16 +2816,16 @@
       </c>
     </row>
     <row customFormat="1" ht="38" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>256</v>
+      <c r="A2" t="s" s="6">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="6">
+        <v>303</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="6">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
@@ -2717,7 +2843,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD9BFD0-F930-4BCA-9C93-2C0B0F9DCF4B}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="16.0" collapsed="true"/>
@@ -2747,11 +2873,11 @@
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="78" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>265</v>
+      <c r="A2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>313</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>14</v>
@@ -2767,8 +2893,8 @@
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="19" r="3" s="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3"/>
-      <c r="B3"/>
+      <c r="A3" s="0"/>
+      <c r="B3" s="0"/>
       <c r="C3" s="7"/>
       <c r="D3" s="1"/>
       <c r="E3" s="5"/>
@@ -2786,7 +2912,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D613A990-B35A-40B9-8717-E014B2376EAA}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="16.0" collapsed="true"/>
@@ -2816,11 +2942,11 @@
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="78" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>267</v>
+      <c r="A2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>314</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>56</v>
@@ -2836,8 +2962,8 @@
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="19" r="3" s="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3"/>
-      <c r="B3"/>
+      <c r="A3" s="0"/>
+      <c r="B3" s="0"/>
       <c r="C3" s="7"/>
       <c r="D3" s="1"/>
       <c r="E3" s="5"/>
@@ -2855,7 +2981,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C48FAA-06E6-4269-9430-6E787AF33FF2}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="16.0" collapsed="true"/>
@@ -2885,11 +3011,11 @@
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="78" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>262</v>
+      <c r="A2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>312</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>57</v>
@@ -2920,7 +3046,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B02ABF-6BE7-42F8-924B-66A45432828E}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.81640625" collapsed="true"/>
@@ -2950,11 +3076,11 @@
       </c>
     </row>
     <row customFormat="1" ht="75" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>250</v>
+      <c r="A2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>300</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -2976,7 +3102,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80CBCA1D-16A9-43B0-BA4E-60CC8E0C88C7}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.81640625" collapsed="true"/>
@@ -3006,11 +3132,11 @@
       </c>
     </row>
     <row customFormat="1" ht="75" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>251</v>
+      <c r="A2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>301</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
